--- a/docentes/Mateos Sanchez Jorge - Estadisticos 20222.xlsx
+++ b/docentes/Mateos Sanchez Jorge - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -83,51 +83,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>TENTZOHUA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>BALDERAS</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>LEÓN</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>CID</t>
-  </si>
-  <si>
-    <t>REYLI</t>
-  </si>
-  <si>
-    <t>ALONDRA YURIDIA</t>
-  </si>
-  <si>
-    <t>RUBI</t>
-  </si>
-  <si>
-    <t>JOSE ISAAC</t>
-  </si>
-  <si>
-    <t>AXEL EDUARDO</t>
   </si>
 </sst>
 </file>
@@ -606,19 +561,19 @@
         <v>36</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G5">
-        <v>66.67</v>
+        <v>69.44</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -697,16 +652,19 @@
         <v>42</v>
       </c>
       <c r="D2">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>97.62</v>
+      </c>
+      <c r="H2">
+        <v>8.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -720,16 +678,19 @@
         <v>41</v>
       </c>
       <c r="D3">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>90.23999999999999</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -743,16 +704,19 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
         <v>38</v>
       </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
-        <v>0</v>
+        <v>92.68000000000001</v>
+      </c>
+      <c r="H4">
+        <v>7.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -766,16 +730,19 @@
         <v>36</v>
       </c>
       <c r="D5">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>86.11</v>
+      </c>
+      <c r="H5">
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -789,16 +756,19 @@
         <v>26</v>
       </c>
       <c r="D6">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>96.15000000000001</v>
+      </c>
+      <c r="H6">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -854,16 +824,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G2">
-        <v>92.86</v>
+        <v>97.62</v>
       </c>
       <c r="H2">
-        <v>8.6</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -880,16 +850,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G3">
-        <v>92.68000000000001</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -906,16 +876,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G4">
-        <v>90.23999999999999</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -929,19 +899,19 @@
         <v>36</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G5">
-        <v>66.67</v>
+        <v>86.11</v>
       </c>
       <c r="H5">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -967,7 +937,7 @@
         <v>96.15000000000001</v>
       </c>
       <c r="H6">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -977,7 +947,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1007,121 +977,6 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>20330051920378</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920100</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920107</v>
-      </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>20330051920302</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920292</v>
-      </c>
-      <c r="B6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Mateos Sanchez Jorge - Estadisticos 20222.xlsx
+++ b/docentes/Mateos Sanchez Jorge - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="34">
   <si>
     <t>Mat</t>
   </si>
@@ -83,6 +83,42 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>SANJUAN</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GALVEZ</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MATA</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>GAMBINO</t>
+  </si>
+  <si>
+    <t>ALMA KAREN</t>
+  </si>
+  <si>
+    <t>LUIS CARLOS</t>
+  </si>
+  <si>
+    <t>ANTONIO ABIDAN</t>
+  </si>
+  <si>
+    <t>RUTH</t>
   </si>
 </sst>
 </file>
@@ -850,16 +886,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G3">
-        <v>90.23999999999999</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="H3">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -876,16 +912,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F4">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G4">
-        <v>92.68000000000001</v>
+        <v>78.05</v>
       </c>
       <c r="H4">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -902,16 +938,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G5">
-        <v>86.11</v>
+        <v>91.67</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -928,16 +964,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G6">
-        <v>96.15000000000001</v>
+        <v>92.31</v>
       </c>
       <c r="H6">
-        <v>9</v>
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>
@@ -947,7 +983,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -977,6 +1013,98 @@
         <v>21</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>21330051920103</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>21330051920301</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>20330051920200</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21330051920291</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Mateos Sanchez Jorge - Estadisticos 20222.xlsx
+++ b/docentes/Mateos Sanchez Jorge - Estadisticos 20222.xlsx
@@ -88,37 +88,37 @@
     <t>SANJUAN</t>
   </si>
   <si>
+    <t>GALVEZ</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>GALVEZ</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>GAMBINO</t>
+  </si>
+  <si>
     <t>MATA</t>
   </si>
   <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>GAMBINO</t>
-  </si>
-  <si>
     <t>ALMA KAREN</t>
   </si>
   <si>
+    <t>ANTONIO ABIDAN</t>
+  </si>
+  <si>
+    <t>RUTH</t>
+  </si>
+  <si>
     <t>LUIS CARLOS</t>
-  </si>
-  <si>
-    <t>ANTONIO ABIDAN</t>
-  </si>
-  <si>
-    <t>RUTH</t>
   </si>
 </sst>
 </file>
@@ -1038,7 +1038,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920301</v>
+        <v>20330051920200</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
@@ -1050,10 +1050,10 @@
         <v>31</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1061,7 +1061,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920200</v>
+        <v>21330051920291</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
@@ -1073,18 +1073,18 @@
         <v>32</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920291</v>
+        <v>21330051920301</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
